--- a/samples/input/見積書_サンプル商事.xlsx
+++ b/samples/input/見積書_サンプル商事.xlsx
@@ -176,6 +176,16 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="窓口一覧" displayName="窓口一覧" ref="D1:E3" headerRowCount="1">
+  <autoFilter ref="D1:E3"/>
+  <tableColumns count="2">
+    <tableColumn id="4" name="サンプル商事の窓口"/>
+    <tableColumn id="5" name="内線"/>
+  </tableColumns>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -541,6 +551,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;Cサンプル商事 御見積</oddHeader>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rIdDrw1"/>
 </worksheet>
 </file>
@@ -551,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,6 +582,16 @@
         <f>'サンプル商事向け'!B9</f>
         <v/>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>サンプル商事の窓口</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>内線</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -571,8 +599,42 @@
           <t>サンプル商事</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>営業部</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>窓口の数</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>COUNTA(窓口一覧[サンプル商事の窓口])</f>
+        <v/>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>経理部</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>